--- a/data/processed/interpolated_data.xlsx
+++ b/data/processed/interpolated_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,15 +437,10 @@
           <t>σ/σmax</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ε͘΄</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B2" t="n">
         <v>-2.302585092994045</v>
@@ -454,27 +449,21 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3759903993648456</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.172480928696832</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B3" t="n">
         <v>-2.302585092994045</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3098438893011644</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.1993825447932754</v>
       </c>
     </row>
     <row r="4">
@@ -485,47 +474,38 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.172480928696832</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.2262841608897189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1</v>
+        <v>0.175</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5332580588792172</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.2531857769861623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4556661920116557</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.2800873930826058</v>
       </c>
     </row>
     <row r="7">
@@ -533,50 +513,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1</v>
+        <v>0.225</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2954766721638665</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.2923358796069598</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B8" t="n">
-        <v>2.302585092994046</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6358598282129422</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.835263281510686</v>
+        <v>0.3045843661313138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B9" t="n">
-        <v>2.302585092994046</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1</v>
+        <v>0.275</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5521925866882574</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.835263281510686</v>
+        <v>0.3168328526556677</v>
       </c>
     </row>
     <row r="10">
@@ -584,50 +555,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B10" t="n">
-        <v>2.302585092994046</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4062520130068391</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.835263281510686</v>
+        <v>0.3290813391800217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B11" t="n">
-        <v>2.70805020110221</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1</v>
+        <v>0.325</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6682277125556288</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.9</v>
+        <v>0.3349959787869885</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B12" t="n">
-        <v>2.70805020110221</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5906330962153115</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.3409106183939553</v>
       </c>
     </row>
     <row r="13">
@@ -635,50 +597,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B13" t="n">
-        <v>2.70805020110221</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.375</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4494652144562564</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.9</v>
+        <v>0.3468252580009221</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B14" t="n">
         <v>-2.302585092994045</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4937376611954777</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.3527398976078889</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B15" t="n">
         <v>-2.302585092994045</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2</v>
+        <v>0.4249999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3842378574991041</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.3555221021822784</v>
       </c>
     </row>
     <row r="16">
@@ -689,47 +642,38 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2800873930826058</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0.3583043067566678</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2</v>
+        <v>0.475</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6709979154632268</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.3610865113310573</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5589503542979322</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.3638687159054468</v>
       </c>
     </row>
     <row r="19">
@@ -737,50 +681,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2</v>
+        <v>0.525</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4384056130442668</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.3583795899392689</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B20" t="n">
-        <v>2.302585092994046</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8169281458899922</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.835263281510686</v>
+        <v>0.3528904639730912</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B21" t="n">
-        <v>2.302585092994046</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2</v>
+        <v>0.575</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7192392479467548</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.835263281510686</v>
+        <v>0.3474013380069133</v>
       </c>
     </row>
     <row r="22">
@@ -788,50 +723,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B22" t="n">
-        <v>2.302585092994046</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6011148282818972</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.835263281510686</v>
+        <v>0.3419122120407355</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B23" t="n">
-        <v>2.70805020110221</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2</v>
+        <v>0.6249999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8678747849955948</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.9</v>
+        <v>0.3530410303382933</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B24" t="n">
-        <v>2.70805020110221</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7732776037026932</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9</v>
+        <v>0.3641698486358512</v>
       </c>
     </row>
     <row r="25">
@@ -839,50 +765,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B25" t="n">
-        <v>2.70805020110221</v>
+        <v>-2.302585092994045</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6628442448996408</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9</v>
+        <v>0.3752986669334091</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B26" t="n">
         <v>-2.302585092994045</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5525637218678748</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1</v>
+        <v>0.386427485230967</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B27" t="n">
-        <v>-2.302585092994045</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4442580621960414</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.1</v>
+        <v>0.2954766721638665</v>
       </c>
     </row>
     <row r="28">
@@ -890,50 +807,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B28" t="n">
-        <v>-2.302585092994045</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3</v>
+        <v>0.125</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3290813391800217</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.1</v>
+        <v>0.3312089073839666</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7329657942895109</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.3669411426040666</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3</v>
+        <v>0.175</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6090213081520034</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.4026733778241667</v>
       </c>
     </row>
     <row r="31">
@@ -944,47 +852,38 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5000549021702679</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.4384056130442668</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B32" t="n">
-        <v>2.302585092994046</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3</v>
+        <v>0.225</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8947563801297088</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.835263281510686</v>
+        <v>0.4538179353257671</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B33" t="n">
-        <v>2.302585092994046</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7992592483971447</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.835263281510686</v>
+        <v>0.4692302576072674</v>
       </c>
     </row>
     <row r="34">
@@ -992,50 +891,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B34" t="n">
-        <v>2.302585092994046</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3</v>
+        <v>0.275</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6779414252324091</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.835263281510686</v>
+        <v>0.4846425798887677</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B35" t="n">
-        <v>2.70805020110221</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9445345805989173</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.9</v>
+        <v>0.5000549021702679</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B36" t="n">
-        <v>2.70805020110221</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3</v>
+        <v>0.325</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8563208894814949</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.9</v>
+        <v>0.5092940034784758</v>
       </c>
     </row>
     <row r="37">
@@ -1043,50 +933,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B37" t="n">
-        <v>2.70805020110221</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7320653201407521</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.9</v>
+        <v>0.5185331047866837</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B38" t="n">
-        <v>-2.302585092994045</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5769528544851581</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.1</v>
+        <v>0.5277722060948915</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B39" t="n">
-        <v>-2.302585092994045</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0.4</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4667094711568088</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.1</v>
+        <v>0.5370113074030994</v>
       </c>
     </row>
     <row r="40">
@@ -1094,50 +975,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B40" t="n">
-        <v>-2.302585092994045</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4</v>
+        <v>0.4249999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3527398976078889</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.1</v>
+        <v>0.5318091303792999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="D41" t="n">
-        <v>0.756816379386042</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.5266069533555002</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4</v>
+        <v>0.475</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6298867513993071</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.5214047763317007</v>
       </c>
     </row>
     <row r="43">
@@ -1148,47 +1020,38 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5370113074030994</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.516202599307901</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B44" t="n">
-        <v>2.302585092994046</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4</v>
+        <v>0.525</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9298452823673606</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.835263281510686</v>
+        <v>0.5143063359548465</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B45" t="n">
-        <v>2.302585092994046</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8318553826209929</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.835263281510686</v>
+        <v>0.5124100726017921</v>
       </c>
     </row>
     <row r="46">
@@ -1196,50 +1059,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B46" t="n">
-        <v>2.302585092994046</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4</v>
+        <v>0.575</v>
       </c>
       <c r="D46" t="n">
-        <v>0.704694711637916</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.835263281510686</v>
+        <v>0.5105138092487376</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B47" t="n">
-        <v>2.70805020110221</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9754552384962497</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.9</v>
+        <v>0.5086175458956831</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B48" t="n">
-        <v>2.70805020110221</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4</v>
+        <v>0.6249999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>0.8763660733566314</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.9</v>
+        <v>0.5158021800613124</v>
       </c>
     </row>
     <row r="49">
@@ -1247,50 +1101,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B49" t="n">
-        <v>2.70805020110221</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7599773129219459</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.9</v>
+        <v>0.5229868142269416</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B50" t="n">
-        <v>-2.302585092994045</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5847255703235702</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.1</v>
+        <v>0.5301714483925709</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B51" t="n">
-        <v>-2.302585092994045</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4411507215576645</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.1</v>
+        <v>0.5373560825582002</v>
       </c>
     </row>
     <row r="52">
@@ -1298,50 +1143,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B52" t="n">
-        <v>-2.302585092994045</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3638687159054468</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.1</v>
+        <v>0.4062520130068391</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="D53" t="n">
-        <v>0.7534646411693656</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.4549677168256036</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6347048750857791</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.5036834206443681</v>
       </c>
     </row>
     <row r="55">
@@ -1349,50 +1185,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5</v>
+        <v>0.175</v>
       </c>
       <c r="D55" t="n">
-        <v>0.516202599307901</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.5523991244631327</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B56" t="n">
         <v>2.302585092994046</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9459841200927803</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.835263281510686</v>
+        <v>0.6011148282818972</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B57" t="n">
         <v>2.302585092994046</v>
       </c>
       <c r="C57" t="n">
-        <v>0.5</v>
+        <v>0.225</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8480809814867089</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.835263281510686</v>
+        <v>0.6203214775195252</v>
       </c>
     </row>
     <row r="58">
@@ -1403,47 +1230,38 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7542181276317472</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.835263281510686</v>
+        <v>0.6395281267571531</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B59" t="n">
-        <v>2.70805020110221</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5</v>
+        <v>0.275</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9954677778377136</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.9</v>
+        <v>0.6587347759947811</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B60" t="n">
-        <v>2.70805020110221</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9035393744574156</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.9</v>
+        <v>0.6779414252324091</v>
       </c>
     </row>
     <row r="61">
@@ -1451,50 +1269,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B61" t="n">
-        <v>2.70805020110221</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5</v>
+        <v>0.325</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8113673154200383</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.9</v>
+        <v>0.6846297468337857</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B62" t="n">
-        <v>-2.302585092994045</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5875666921712996</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.1</v>
+        <v>0.6913180684351625</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B63" t="n">
-        <v>-2.302585092994045</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6</v>
+        <v>0.375</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4188232570830346</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.1</v>
+        <v>0.6980063900365392</v>
       </c>
     </row>
     <row r="64">
@@ -1502,50 +1311,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B64" t="n">
-        <v>-2.302585092994045</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3419122120407355</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.1</v>
+        <v>0.704694711637916</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6</v>
+        <v>0.4249999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7644795527384661</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.7170755656363738</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6356824653989764</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.7294564196348315</v>
       </c>
     </row>
     <row r="67">
@@ -1553,50 +1353,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6</v>
+        <v>0.475</v>
       </c>
       <c r="D67" t="n">
-        <v>0.5086175458956831</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.7418372736332894</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B68" t="n">
         <v>2.302585092994046</v>
       </c>
       <c r="C68" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9432207690458596</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.835263281510686</v>
+        <v>0.7542181276317472</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B69" t="n">
         <v>2.302585092994046</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6</v>
+        <v>0.525</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8436328146343873</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.835263281510686</v>
+        <v>0.7458758126874114</v>
       </c>
     </row>
     <row r="70">
@@ -1607,47 +1398,38 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7208488678544041</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.835263281510686</v>
+        <v>0.7375334977430756</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B71" t="n">
-        <v>2.70805020110221</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6</v>
+        <v>0.575</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.9</v>
+        <v>0.7291911827987398</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B72" t="n">
-        <v>2.70805020110221</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C72" t="n">
         <v>0.6</v>
       </c>
       <c r="D72" t="n">
-        <v>0.8881465166973299</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.9</v>
+        <v>0.7208488678544041</v>
       </c>
     </row>
     <row r="73">
@@ -1655,50 +1437,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B73" t="n">
-        <v>2.70805020110221</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6</v>
+        <v>0.6249999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>0.7768658838612233</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.9</v>
+        <v>0.7196995446000268</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B74" t="n">
-        <v>-2.302585092994045</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C74" t="n">
-        <v>0.7</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5913330334225908</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.1</v>
+        <v>0.7185502213456496</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B75" t="n">
-        <v>-2.302585092994045</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>0.5023592221942329</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.1</v>
+        <v>0.7174008980912724</v>
       </c>
     </row>
     <row r="76">
@@ -1706,50 +1479,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B76" t="n">
-        <v>-2.302585092994045</v>
+        <v>2.302585092994046</v>
       </c>
       <c r="C76" t="n">
         <v>0.7</v>
       </c>
       <c r="D76" t="n">
-        <v>0.386427485230967</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.1</v>
+        <v>0.7162515748368952</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>2.70805020110221</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="D77" t="n">
-        <v>0.7775028886920906</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.4494652144562564</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>2.70805020110221</v>
       </c>
       <c r="C78" t="n">
-        <v>0.7</v>
+        <v>0.125</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6780156173543928</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.5028099720671025</v>
       </c>
     </row>
     <row r="79">
@@ -1757,50 +1521,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>2.70805020110221</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="D79" t="n">
-        <v>0.5373560825582002</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.4676316407553429</v>
+        <v>0.5561547296779485</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B80" t="n">
-        <v>2.302585092994046</v>
+        <v>2.70805020110221</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7</v>
+        <v>0.175</v>
       </c>
       <c r="D80" t="n">
-        <v>0.937795142807615</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.835263281510686</v>
+        <v>0.6094994872887947</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B81" t="n">
-        <v>2.302585092994046</v>
+        <v>2.70805020110221</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8369991224381241</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.835263281510686</v>
+        <v>0.6628442448996408</v>
       </c>
     </row>
     <row r="82">
@@ -1808,50 +1563,41 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B82" t="n">
-        <v>2.302585092994046</v>
+        <v>2.70805020110221</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7</v>
+        <v>0.225</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7162515748368952</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.835263281510686</v>
+        <v>0.6801495137099186</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.0008176614881439084</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B83" t="n">
         <v>2.70805020110221</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9776339119795139</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.9</v>
+        <v>0.6974547825201964</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.0007855459544383347</v>
+        <v>0.0007558578987150416</v>
       </c>
       <c r="B84" t="n">
         <v>2.70805020110221</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7</v>
+        <v>0.275</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8654767646858068</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.9</v>
+        <v>0.7147600513304743</v>
       </c>
     </row>
     <row r="85">
@@ -1862,13 +1608,3034 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C85" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.7320653201407521</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.7390433183360505</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.746021316531349</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.7529993147266475</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B89" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.7599773129219459</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.7728248135464689</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B91" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.785672314170992</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.7985198147955151</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B93" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.8113673154200383</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.8027419575303345</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.7941165996406309</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B96" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.7854912417509271</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.7768658838612233</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.7736812088462846</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.7704965338313458</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.767311858816407</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>0.0007558578987150416</v>
+      </c>
+      <c r="B101" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C101" t="n">
         <v>0.7</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D101" t="n">
         <v>0.7641271838014682</v>
       </c>
-      <c r="E85" t="n">
-        <v>0.9</v>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B102" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.3098438893011644</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B103" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.3284423813506493</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B104" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.3470408734001342</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B105" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.3656393654496191</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B106" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.3842378574991041</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B107" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.3992429086733384</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B108" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.4142479598475727</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B109" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.4292530110218071</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B110" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.4442580621960414</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B111" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.4498709144362333</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B112" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.4554837666764251</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B113" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.461096618916617</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B114" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.4667094711568088</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B115" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.4603197837570228</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B116" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.4539300963572367</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B117" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.4475404089574506</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B118" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.4411507215576645</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B119" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.435568855439007</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B120" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4299869893203496</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B121" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.424405123201692</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B122" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4188232570830346</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B123" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.4397072483608341</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B124" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4605912396386337</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B125" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.4814752309164333</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.5023592221942329</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.4556661920116557</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4814872325832248</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.5073082731547939</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5331293137263631</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.5589503542979322</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.5714680927614499</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5839858312249677</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.5965035696884856</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.6090213081520034</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.6142376689638293</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6194540297756552</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6246703905874811</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.6298867513993071</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.631091282320925</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.632295813242543</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.6335003441641611</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.6347048750857791</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.6349492726640784</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.6351936702423777</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.6354380678206771</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.6356824653989764</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.6462657533878304</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.6568490413766845</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.6674323293655386</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.6780156173543928</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.5521925866882574</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.5939542520028818</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.6357159173175061</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.6774775826321304</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.7192392479467548</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.7392442480593522</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.7592492481719497</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.7792542482845473</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.7992592483971447</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.8074082819531068</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B162" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.8155573155090687</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.8237063490650308</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.8318553826209929</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B165" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.8359117823374219</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B166" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.8399681820538508</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B167" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.8440245817702798</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B168" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.8480809814867089</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B169" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.8469689397736284</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.8458568980605481</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B171" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.8447448563474678</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.8436328146343873</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B173" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.8419743915853215</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B174" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.8403159685362558</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.83865754548719</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B176" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.8369991224381241</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.5906330962153115</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B178" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.6362942230871569</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B179" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.6819553499590023</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.7276164768308477</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.7732776037026932</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.7940384251473935</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.814799246592094</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.8355600680367945</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.8563208894814949</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.861332185450279</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.8663434814190631</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.8713547773878473</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.8763660733566314</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.8831593986318275</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.8899527239070235</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.8967460491822196</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.9035393744574156</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.8996911600173941</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.8958429455773728</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.8919947311373514</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.8881465166973299</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.8824790786944492</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.8768116406915684</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.8711442026886876</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>0.0007855459544383347</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.8654767646858068</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B202" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.3759903993648456</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B203" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.4054272148225037</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B204" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.4348640302801617</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B205" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.4643008457378197</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B206" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.4937376611954777</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B207" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.508444176363577</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B208" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.5231506915316763</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B209" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.5378572066997755</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B210" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.5525637218678748</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B211" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.5586610050221956</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B212" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.5647582881765164</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B213" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.5708555713308373</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B214" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.5769528544851581</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B215" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.5788960334447611</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B216" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.5808392124043641</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B217" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.5827823913639671</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B218" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.5847255703235702</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B219" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.5854358507855025</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B220" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.5861461312474349</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B221" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.5868564117093673</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B222" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.5875666921712996</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B223" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.5885082774841224</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B224" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.5894498627969452</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B225" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.590391448109768</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B226" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.5913330334225908</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.5332580588792172</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.5676930230252196</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.602127987171222</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.6365629513172244</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.6709979154632268</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.6864898851697978</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.7019818548763689</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.71747382458294</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.7329657942895109</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.7389284405636437</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.7448910868377764</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.7508537331119092</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.756816379386042</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.7559784448318729</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.7551405102777038</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.7543025757235348</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.7534646411693656</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.7562183690616407</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.7589720969539159</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.761725824846191</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.7644795527384661</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.7677353867268722</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.7709912207152784</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.7742470547036845</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.7775028886920906</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B252" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.6358598282129422</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B253" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.6811269076322046</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B254" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.7263939870514672</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B255" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.7716610664707296</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B256" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.8169281458899922</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B257" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.8363852044499214</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.8558422630098506</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B259" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.8752993215697797</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B260" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.8947563801297088</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B261" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.9035286056891217</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B262" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.9123008312485347</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B263" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.9210730568079477</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B264" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.9298452823673606</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B265" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.9338799917987155</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B266" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.9379147012300705</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B267" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.9419494106614253</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B268" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.9459841200927803</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B269" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.9452932823310501</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B270" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.94460244456932</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B271" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.9439116068075898</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B272" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.9432207690458596</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B273" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.9418643624862985</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B274" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.9405079559267373</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B275" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.9391515493671762</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B276" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.937795142807615</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B277" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.6682277125556288</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B278" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.7181394806656203</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B279" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.7680512487756118</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B280" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.8179630168856032</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B281" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.8678747849955948</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B282" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.8870397338964254</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B283" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.9062046827972561</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B284" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.9253696316980866</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B285" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.9445345805989173</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B286" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.9522647450732503</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0.9599949095475835</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B288" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.9677250740219165</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B289" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0.9754552384962497</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B290" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.4249999999999999</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.9804583733316157</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B291" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.9854615081669816</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B292" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.9904646430023476</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B293" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.9954677778377136</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B294" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.9966008333782852</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B295" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.9977338889188567</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B296" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.9988669444594284</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B297" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B298" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.9944084779948785</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B299" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.9888169559897569</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B300" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.9832254339846355</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>0.0008176614881439084</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.9776339119795139</v>
       </c>
     </row>
   </sheetData>
